--- a/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="39">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,12 @@
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
@@ -97,7 +103,10 @@
     <t>MANI</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -110,6 +119,12 @@
   </si>
   <si>
     <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAID</t>
+  </si>
+  <si>
+    <t>JAVIER FERNANDO</t>
   </si>
   <si>
     <t>DANIEL</t>
@@ -968,7 +983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1006,10 +1021,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1023,70 +1038,116 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920287</v>
+        <v>20330051920318</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920292</v>
+        <v>19330051920258</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920261</v>
+        <v>20330051920287</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920292</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920261</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F7" t="s">
         <v>15</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
@@ -88,12 +88,12 @@
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
@@ -103,12 +103,12 @@
     <t>MANI</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -121,10 +121,10 @@
     <t>VICTOR MANUEL</t>
   </si>
   <si>
+    <t>JAVIER FERNANDO</t>
+  </si>
+  <si>
     <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>JAVIER FERNANDO</t>
   </si>
   <si>
     <t>DANIEL</t>
@@ -1021,7 +1021,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920318</v>
+        <v>19330051920258</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1050,10 +1050,10 @@
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920258</v>
+        <v>20330051920318</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1073,13 +1073,13 @@
         <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">

--- a/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
@@ -85,49 +85,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>CABRERA</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
     <t>MANI</t>
   </si>
   <si>
-    <t>DOMINGUEZ</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>GAMBOA</t>
   </si>
   <si>
     <t>ZAPATA</t>
   </si>
   <si>
+    <t>EDGAR DANIEL</t>
+  </si>
+  <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
-    <t>JAVIER FERNANDO</t>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
   </si>
   <si>
     <t>VALERIA ANGELY</t>
@@ -1015,13 +1015,13 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920382</v>
+        <v>20330051920381</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1038,22 +1038,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920258</v>
+        <v>20330051920382</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920318</v>
+        <v>20330051920287</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1073,18 +1073,18 @@
         <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920287</v>
+        <v>20330051920318</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1096,10 +1096,10 @@
         <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>1</v>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="169">
   <si>
     <t>Mat</t>
   </si>
@@ -85,55 +85,445 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ADELL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>XOCUA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
+    <t>GASCA</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>BUENO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>COLOTL</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>NAMIGTLE</t>
+  </si>
+  <si>
+    <t>XILCAHUA</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CARAZA</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>MANI</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>PALMA</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>GUZMAN</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>VINALAY</t>
+  </si>
+  <si>
+    <t>YOPIHUA</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
+    <t>VILLALBA</t>
+  </si>
+  <si>
+    <t>AGUIRRE</t>
+  </si>
+  <si>
+    <t>TLAXCALA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>GAMBOA</t>
   </si>
   <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>MONTERROSAS</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>ARENZANO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>CUAHUA</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
     <t>ZAPATA</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>CRISTOPHER ALAIN</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>OCTAVIO</t>
+  </si>
+  <si>
+    <t>JOSE ABRAHAM</t>
+  </si>
+  <si>
+    <t>JOSE MATEO</t>
+  </si>
+  <si>
+    <t>MARCOS URIEL</t>
+  </si>
+  <si>
     <t>EDGAR DANIEL</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
+  </si>
+  <si>
+    <t>AMERICA MICHELLE</t>
+  </si>
+  <si>
     <t>DANIEL</t>
   </si>
   <si>
+    <t>STEPHANIE</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
+    <t>NAOMI</t>
+  </si>
+  <si>
+    <t>ZULEICA RENATA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>CRISTIAN</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>ALFREDO</t>
+  </si>
+  <si>
+    <t>CESAR JAHIR</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>JORGE LUIS</t>
+  </si>
+  <si>
+    <t>MISAEL</t>
+  </si>
+  <si>
+    <t>ALMA RUBI</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>IGNACIO</t>
+  </si>
+  <si>
+    <t>ALEXIS MANUEL</t>
+  </si>
+  <si>
+    <t>DIEGO ADELFO</t>
+  </si>
+  <si>
+    <t>JESUS HAZAEL</t>
+  </si>
+  <si>
+    <t>ANGEL SAID</t>
+  </si>
+  <si>
+    <t>LUIS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>OMAR</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>ADAN</t>
+  </si>
+  <si>
+    <t>MARIAM GUADALUPE</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ANGEL ALDAHIR</t>
+  </si>
+  <si>
+    <t>ESTEFANI</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>ANGELA MONTSERRAT</t>
+  </si>
+  <si>
     <t>GUILLERMO SAID</t>
   </si>
   <si>
+    <t>VICTOR HUGO</t>
+  </si>
+  <si>
+    <t>KAREN ESTEPHANY</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>JARED URIEL</t>
+  </si>
+  <si>
     <t>VALERIA ANGELY</t>
   </si>
   <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>MARIA MAGDALENA</t>
+  </si>
+  <si>
+    <t>IKER</t>
+  </si>
+  <si>
+    <t>IVONNE SHERLINE</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>JOSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>ANEL</t>
+  </si>
+  <si>
+    <t>LAURA IVETTE</t>
+  </si>
+  <si>
+    <t>ERICA</t>
+  </si>
+  <si>
+    <t>WENDY</t>
+  </si>
+  <si>
     <t>JUAN CARLOS</t>
+  </si>
+  <si>
+    <t>CESAR JOVANI</t>
   </si>
 </sst>
 </file>
@@ -703,16 +1093,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>15.63</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -726,16 +1119,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H3">
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -749,16 +1145,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>28.13</v>
+      </c>
+      <c r="H4">
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -772,16 +1171,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>57.89</v>
+      </c>
+      <c r="H5">
+        <v>6.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -795,16 +1197,19 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -860,16 +1265,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>96.88</v>
+        <v>15.63</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -886,16 +1291,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>33.33</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -912,16 +1317,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="G4">
-        <v>93.75</v>
+        <v>28.13</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -938,16 +1343,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>68.42</v>
+        <v>57.89</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -964,16 +1369,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1015,22 +1420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920381</v>
+        <v>20330051920002</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1038,22 +1443,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920382</v>
+        <v>20330051920013</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1061,22 +1466,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920287</v>
+        <v>20330051920021</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1084,70 +1489,1381 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920318</v>
+        <v>20330051920026</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920292</v>
+        <v>20330051920029</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920261</v>
+        <v>20330051920035</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920381</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920382</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920329</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920335</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920286</v>
+      </c>
+      <c r="B12" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920287</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920293</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920298</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920312</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>122</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920379</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>19330051920251</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>19330051920433</v>
+      </c>
+      <c r="B19" t="s">
         <v>38</v>
       </c>
-      <c r="E7" t="s">
+      <c r="C19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F19" t="s">
         <v>15</v>
       </c>
-      <c r="G7">
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920257</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920402</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>81</v>
+      </c>
+      <c r="D21" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920411</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D22" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920361</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920004</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920006</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920007</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920009</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920011</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920012</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920014</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920017</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31" t="s">
+        <v>137</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920023</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920060</v>
+      </c>
+      <c r="B33" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" t="s">
+        <v>139</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920027</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920031</v>
+      </c>
+      <c r="B35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>20330051920032</v>
+      </c>
+      <c r="B36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920036</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" t="s">
+        <v>142</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920337</v>
+      </c>
+      <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920344</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920347</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" t="s">
+        <v>145</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920349</v>
+      </c>
+      <c r="B41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>20330051920350</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>20330051920352</v>
+      </c>
+      <c r="B43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>20330051920357</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" t="s">
+        <v>109</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>20330051920383</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D45" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>20330051920318</v>
+      </c>
+      <c r="B46" t="s">
+        <v>57</v>
+      </c>
+      <c r="C46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" t="s">
+        <v>150</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>20330051920396</v>
+      </c>
+      <c r="B47" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" t="s">
+        <v>151</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>20330051920283</v>
+      </c>
+      <c r="B48" t="s">
+        <v>59</v>
+      </c>
+      <c r="C48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D48" t="s">
+        <v>152</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>20330051920284</v>
+      </c>
+      <c r="B49" t="s">
+        <v>60</v>
+      </c>
+      <c r="C49" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>20330051920390</v>
+      </c>
+      <c r="B50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C50" t="s">
+        <v>37</v>
+      </c>
+      <c r="D50" t="s">
+        <v>154</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>20330051920292</v>
+      </c>
+      <c r="B51" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" t="s">
+        <v>155</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>20330051920394</v>
+      </c>
+      <c r="B52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52" t="s">
+        <v>156</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>20330051920296</v>
+      </c>
+      <c r="B53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" t="s">
+        <v>99</v>
+      </c>
+      <c r="D53" t="s">
+        <v>157</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>20330051920299</v>
+      </c>
+      <c r="B54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" t="s">
+        <v>158</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>20330051920300</v>
+      </c>
+      <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>101</v>
+      </c>
+      <c r="D55" t="s">
+        <v>159</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>13</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>20330051920303</v>
+      </c>
+      <c r="B56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" t="s">
+        <v>79</v>
+      </c>
+      <c r="D56" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>20330051920308</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57" t="s">
+        <v>40</v>
+      </c>
+      <c r="D57" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>13</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
+        <v>20330051920313</v>
+      </c>
+      <c r="B58" t="s">
+        <v>36</v>
+      </c>
+      <c r="C58" t="s">
+        <v>31</v>
+      </c>
+      <c r="D58" t="s">
+        <v>162</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>20330051920314</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" t="s">
+        <v>102</v>
+      </c>
+      <c r="D59" t="s">
+        <v>163</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>20330051920316</v>
+      </c>
+      <c r="B60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" t="s">
+        <v>103</v>
+      </c>
+      <c r="D60" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>19330051920256</v>
+      </c>
+      <c r="B61" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61" t="s">
+        <v>10</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>19330051920255</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" t="s">
+        <v>105</v>
+      </c>
+      <c r="D62" t="s">
+        <v>166</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>19330051920261</v>
+      </c>
+      <c r="B63" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" t="s">
+        <v>167</v>
+      </c>
+      <c r="E63" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>19330051920405</v>
+      </c>
+      <c r="B64" t="s">
+        <v>67</v>
+      </c>
+      <c r="C64" t="s">
+        <v>107</v>
+      </c>
+      <c r="D64" t="s">
+        <v>168</v>
+      </c>
+      <c r="E64" t="s">
+        <v>10</v>
+      </c>
+      <c r="F64" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="171">
   <si>
     <t>Mat</t>
   </si>
@@ -109,6 +109,9 @@
     <t>VASQUEZ</t>
   </si>
   <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -232,6 +235,9 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>MONTALVO</t>
   </si>
   <si>
@@ -241,9 +247,6 @@
     <t>OSORIO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
@@ -365,6 +368,9 @@
   </si>
   <si>
     <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
   </si>
   <si>
     <t>JUAN GUILLERMO</t>
@@ -1388,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1426,10 +1432,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1449,10 +1455,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1472,10 +1478,10 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1495,10 +1501,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1518,10 +1524,10 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1541,10 +1547,10 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1564,10 +1570,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1590,7 +1596,7 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1604,16 +1610,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920329</v>
+        <v>20330051920397</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1627,16 +1633,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920335</v>
+        <v>20330051920329</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1650,22 +1656,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920286</v>
+        <v>20330051920335</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1673,16 +1679,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920287</v>
+        <v>20330051920286</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1696,16 +1702,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920293</v>
+        <v>20330051920287</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1719,16 +1725,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920298</v>
+        <v>20330051920293</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1742,7 +1748,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920312</v>
+        <v>20330051920298</v>
       </c>
       <c r="B16" t="s">
         <v>36</v>
@@ -1751,7 +1757,7 @@
         <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1765,16 +1771,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920379</v>
+        <v>20330051920312</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
         <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1788,7 +1794,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920251</v>
+        <v>20330051920379</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
@@ -1797,13 +1803,13 @@
         <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -1811,7 +1817,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920433</v>
+        <v>19330051920251</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
@@ -1820,7 +1826,7 @@
         <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -1834,16 +1840,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920257</v>
+        <v>19330051920433</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -1857,16 +1863,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920402</v>
+        <v>19330051920257</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -1880,7 +1886,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920411</v>
+        <v>19330051920402</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
@@ -1889,7 +1895,7 @@
         <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -1903,7 +1909,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920361</v>
+        <v>19330051920411</v>
       </c>
       <c r="B23" t="s">
         <v>41</v>
@@ -1912,21 +1918,21 @@
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920004</v>
+        <v>20330051920361</v>
       </c>
       <c r="B24" t="s">
         <v>42</v>
@@ -1935,7 +1941,7 @@
         <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1949,7 +1955,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920006</v>
+        <v>20330051920004</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
@@ -1958,7 +1964,7 @@
         <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1972,16 +1978,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920007</v>
+        <v>20330051920006</v>
       </c>
       <c r="B26" t="s">
         <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1995,16 +2001,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920009</v>
+        <v>20330051920007</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -2018,16 +2024,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920011</v>
+        <v>20330051920009</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2041,16 +2047,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920012</v>
+        <v>20330051920011</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -2064,16 +2070,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920014</v>
+        <v>20330051920012</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2087,7 +2093,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920017</v>
+        <v>20330051920014</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -2096,7 +2102,7 @@
         <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2110,7 +2116,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920023</v>
+        <v>20330051920017</v>
       </c>
       <c r="B32" t="s">
         <v>48</v>
@@ -2119,7 +2125,7 @@
         <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -2133,7 +2139,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920060</v>
+        <v>20330051920023</v>
       </c>
       <c r="B33" t="s">
         <v>49</v>
@@ -2142,7 +2148,7 @@
         <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2156,16 +2162,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920027</v>
+        <v>20330051920060</v>
       </c>
       <c r="B34" t="s">
         <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -2179,16 +2185,16 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920031</v>
+        <v>20330051920027</v>
       </c>
       <c r="B35" t="s">
         <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -2202,7 +2208,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920032</v>
+        <v>20330051920031</v>
       </c>
       <c r="B36" t="s">
         <v>52</v>
@@ -2211,7 +2217,7 @@
         <v>92</v>
       </c>
       <c r="D36" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E36" t="s">
         <v>8</v>
@@ -2225,16 +2231,16 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920036</v>
+        <v>20330051920032</v>
       </c>
       <c r="B37" t="s">
         <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -2248,22 +2254,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920337</v>
+        <v>20330051920036</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2271,16 +2277,16 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920344</v>
+        <v>20330051920337</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
         <v>94</v>
       </c>
       <c r="D39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -2294,16 +2300,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>20330051920347</v>
+        <v>20330051920344</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2317,7 +2323,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>20330051920349</v>
+        <v>20330051920347</v>
       </c>
       <c r="B41" t="s">
         <v>55</v>
@@ -2326,7 +2332,7 @@
         <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -2340,16 +2346,16 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>20330051920350</v>
+        <v>20330051920349</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -2363,16 +2369,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>20330051920352</v>
+        <v>20330051920350</v>
       </c>
       <c r="B43" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="D43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2386,16 +2392,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>20330051920357</v>
+        <v>20330051920352</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D44" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2409,16 +2415,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>20330051920383</v>
+        <v>20330051920357</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C45" t="s">
         <v>96</v>
       </c>
       <c r="D45" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2432,22 +2438,22 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>20330051920318</v>
+        <v>20330051920383</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
         <v>97</v>
       </c>
       <c r="D46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2455,16 +2461,16 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>20330051920396</v>
+        <v>20330051920318</v>
       </c>
       <c r="B47" t="s">
         <v>58</v>
       </c>
       <c r="C47" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="D47" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E47" t="s">
         <v>9</v>
@@ -2478,22 +2484,22 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>20330051920283</v>
+        <v>20330051920396</v>
       </c>
       <c r="B48" t="s">
         <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2501,16 +2507,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>20330051920284</v>
+        <v>20330051920283</v>
       </c>
       <c r="B49" t="s">
         <v>60</v>
       </c>
       <c r="C49" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="D49" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2524,16 +2530,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>20330051920390</v>
+        <v>20330051920284</v>
       </c>
       <c r="B50" t="s">
         <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2547,16 +2553,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>20330051920292</v>
+        <v>20330051920390</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="D51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2570,16 +2576,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>20330051920394</v>
+        <v>20330051920292</v>
       </c>
       <c r="B52" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D52" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2593,16 +2599,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>20330051920296</v>
+        <v>20330051920394</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2616,16 +2622,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>20330051920299</v>
+        <v>20330051920296</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
         <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2639,16 +2645,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>20330051920300</v>
+        <v>20330051920299</v>
       </c>
       <c r="B55" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
         <v>101</v>
       </c>
       <c r="D55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2662,16 +2668,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>20330051920303</v>
+        <v>20330051920300</v>
       </c>
       <c r="B56" t="s">
         <v>63</v>
       </c>
       <c r="C56" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2685,16 +2691,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>20330051920308</v>
+        <v>20330051920303</v>
       </c>
       <c r="B57" t="s">
         <v>64</v>
       </c>
       <c r="C57" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2708,16 +2714,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>20330051920313</v>
+        <v>20330051920308</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D58" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2731,16 +2737,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>20330051920314</v>
+        <v>20330051920313</v>
       </c>
       <c r="B59" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="D59" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2754,16 +2760,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>20330051920316</v>
+        <v>20330051920314</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C60" t="s">
         <v>103</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2777,22 +2783,22 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>19330051920256</v>
+        <v>20330051920316</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
         <v>104</v>
       </c>
       <c r="D61" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2800,7 +2806,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>19330051920255</v>
+        <v>19330051920256</v>
       </c>
       <c r="B62" t="s">
         <v>28</v>
@@ -2809,7 +2815,7 @@
         <v>105</v>
       </c>
       <c r="D62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -2823,16 +2829,16 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>19330051920261</v>
+        <v>19330051920255</v>
       </c>
       <c r="B63" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="C63" t="s">
         <v>106</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
@@ -2846,7 +2852,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>19330051920405</v>
+        <v>19330051920261</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
@@ -2855,7 +2861,7 @@
         <v>107</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -2864,6 +2870,29 @@
         <v>15</v>
       </c>
       <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>19330051920405</v>
+      </c>
+      <c r="B65" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" t="s">
+        <v>170</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
+        <v>15</v>
+      </c>
+      <c r="G65">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
+++ b/docentes/Medina Tolentino Elio - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -842,7 +833,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -868,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -894,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -911,16 +902,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>94.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -946,7 +937,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -986,29 +977,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920397</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
